--- a/Data/Building/MeetingRoomTwo.HumanState.xlsx
+++ b/Data/Building/MeetingRoomTwo.HumanState.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709260085</v>
+        <v>1711852376</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709261471</v>
+        <v>1711852984</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +562,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709272795</v>
+        <v>1711853050</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +576,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709274256</v>
+        <v>1711854362</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +609,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709252122</v>
+        <v>1711864700</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +642,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709253337</v>
+        <v>1711866413</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +675,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +698,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709253363</v>
+        <v>1711867055</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +712,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +731,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709254854</v>
+        <v>1711868807</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +745,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +768,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709265325</v>
+        <v>1711931544</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +782,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +801,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709266068</v>
+        <v>1711932094</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +815,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +838,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709266579</v>
+        <v>1711942008</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +852,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +871,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709267604</v>
+        <v>1711944794</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +885,11 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +908,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709339388</v>
+        <v>1712018892</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +922,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +941,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709341509</v>
+        <v>1712020804</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +955,11 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +978,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709353148</v>
+        <v>1712031637</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +992,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1011,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709354424</v>
+        <v>1712033782</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1025,11 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1048,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709425869</v>
+        <v>1712105456</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1062,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1081,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709427434</v>
+        <v>1712106937</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1095,11 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1118,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709438545</v>
+        <v>1712119379</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1132,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1151,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709439574</v>
+        <v>1712120359</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1165,11 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1188,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709440820</v>
+        <v>1712120485</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1202,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1221,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709441688</v>
+        <v>1712121752</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1235,11 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1258,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709512280</v>
+        <v>1712189149</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1272,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709513121</v>
+        <v>1712190925</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1305,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1328,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709513356</v>
+        <v>1712204739</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1342,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1361,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709514436</v>
+        <v>1712206626</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1375,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1394,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709524209</v>
+        <v>1712276004</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1408,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709525660</v>
+        <v>1712278875</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1441,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1460,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709526724</v>
+        <v>1712289050</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1474,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1493,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709528232</v>
+        <v>1712292521</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1507,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1526,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709599411</v>
+        <v>1712538181</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1540,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1559,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709601183</v>
+        <v>1712539944</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1573,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1592,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709614275</v>
+        <v>1712548370</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1606,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1625,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709617134</v>
+        <v>1712549169</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1639,11 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1662,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709855690</v>
+        <v>1712550680</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1676,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1695,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709857086</v>
+        <v>1712551401</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1709,11 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1732,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709867527</v>
+        <v>1712624446</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1746,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1765,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709869452</v>
+        <v>1712625918</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1779,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1802,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709944872</v>
+        <v>1712636669</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1816,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709946719</v>
+        <v>1712638338</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1849,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1868,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709955182</v>
+        <v>1712710894</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1882,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1901,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709957745</v>
+        <v>1712711612</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1915,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1938,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710032514</v>
+        <v>1712712327</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1952,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710033877</v>
+        <v>1712714133</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1985,11 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +2008,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710043449</v>
+        <v>1712722654</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2022,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2041,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710045684</v>
+        <v>1712723966</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2055,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2078,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710047062</v>
+        <v>1712724194</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2092,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2111,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710048955</v>
+        <v>1712725681</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2125,11 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2148,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710117918</v>
+        <v>1712798459</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2162,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2181,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710120243</v>
+        <v>1712799441</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2195,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2214,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710132456</v>
+        <v>1712808067</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2228,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2247,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710134030</v>
+        <v>1712808788</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2261,11 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2284,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710204339</v>
+        <v>1712809381</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2298,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2317,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710205728</v>
+        <v>1712810647</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2331,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2354,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710217968</v>
+        <v>1712883618</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2368,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2387,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710220584</v>
+        <v>1712885658</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2401,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2424,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710463403</v>
+        <v>1712896082</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2438,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2457,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710464952</v>
+        <v>1712897777</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2471,11 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2494,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710475012</v>
+        <v>1713140694</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2508,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2527,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710475860</v>
+        <v>1713141645</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2541,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2560,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710548457</v>
+        <v>1713152294</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2574,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2593,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710549561</v>
+        <v>1713154184</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2607,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2630,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710562961</v>
+        <v>1713226272</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2644,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2663,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710564801</v>
+        <v>1713227872</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2677,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2696,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710637230</v>
+        <v>1713238166</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2710,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2729,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710639205</v>
+        <v>1713239202</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2743,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2766,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710650459</v>
+        <v>1713314241</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2780,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2799,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710651746</v>
+        <v>1713315975</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2813,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2836,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710722300</v>
+        <v>1713325097</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2850,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2869,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710723975</v>
+        <v>1713325546</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2883,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2902,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710734876</v>
+        <v>1713326131</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2916,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2935,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710736488</v>
+        <v>1713326943</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2949,11 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2972,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710808622</v>
+        <v>1713398072</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2986,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +3005,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710810933</v>
+        <v>1713399482</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +3019,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3042,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710821996</v>
+        <v>1713409302</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3056,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3075,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710823309</v>
+        <v>1713409848</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3089,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3108,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1711067399</v>
+        <v>1713410075</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3122,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3141,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1711069248</v>
+        <v>1713411005</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3155,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3174,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1711080564</v>
+        <v>1713487270</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3188,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3207,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1711081057</v>
+        <v>1713488095</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3221,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3240,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1711081538</v>
+        <v>1713498549</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3254,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3273,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1711082538</v>
+        <v>1713499963</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3287,11 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3310,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1711153777</v>
+        <v>1713744660</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3324,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3343,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1711155280</v>
+        <v>1713746421</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3357,11 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3380,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1711167569</v>
+        <v>1713754630</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3394,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3413,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1711169981</v>
+        <v>1713755493</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3427,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3446,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1711239539</v>
+        <v>1713755505</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3460,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3479,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1711240727</v>
+        <v>1713756987</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3493,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3512,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1711240896</v>
+        <v>1713832703</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3526,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3545,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1711241948</v>
+        <v>1713834549</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3559,11 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3582,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1711251598</v>
+        <v>1713846077</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3596,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3615,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1711254909</v>
+        <v>1713846696</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3629,11 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3652,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1711326219</v>
+        <v>1713847126</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3666,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3685,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1711327668</v>
+        <v>1713847938</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3699,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3722,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1711338563</v>
+        <v>1713918098</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3736,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3755,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1711340770</v>
+        <v>1713919574</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3769,11 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3792,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1711414202</v>
+        <v>1713931324</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3806,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3825,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1711416009</v>
+        <v>1713932952</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3839,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3858,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1711426615</v>
+        <v>1714002453</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3872,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3891,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711429217</v>
+        <v>1714003784</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3905,287 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1714014474</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1714016640</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1714089516</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1714090409</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1714099734</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1714100387</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1714101758</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1714102974</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
